--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="509">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -598,6 +598,9 @@
 This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
+    <t>completed</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -617,7 +620,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>1539: fixed value = completed</t>
+    <t>1539: fixed value = #completed</t>
   </si>
   <si>
     <t>Procedure.statusReason</t>
@@ -805,6 +808,9 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
+    <t>371883000</t>
+  </si>
+  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -814,7 +820,7 @@
     <t>C*E.1</t>
   </si>
   <si>
-    <t>1314: fixed value = 371883000</t>
+    <t>1314: fixed value = #371883000</t>
   </si>
   <si>
     <t>Procedure.category.coding.display</t>
@@ -3815,7 +3821,7 @@
         <v>79</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>79</v>
@@ -3830,11 +3836,11 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -3861,25 +3867,25 @@
         <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>79</v>
@@ -3887,14 +3893,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3913,16 +3919,16 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3948,13 +3954,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3972,7 +3978,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3987,10 +3993,10 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -4007,10 +4013,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4033,13 +4039,13 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4066,13 +4072,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -4090,7 +4096,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4108,10 +4114,10 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>79</v>
@@ -4125,10 +4131,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4151,13 +4157,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4208,7 +4214,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4226,7 +4232,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4243,10 +4249,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4275,7 +4281,7 @@
         <v>136</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>138</v>
@@ -4316,19 +4322,19 @@
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4346,7 +4352,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4363,10 +4369,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4389,19 +4395,19 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4450,7 +4456,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4468,13 +4474,13 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4485,10 +4491,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4511,13 +4517,13 @@
         <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4568,7 +4574,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4586,7 +4592,7 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
@@ -4603,10 +4609,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4635,7 +4641,7 @@
         <v>136</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>138</v>
@@ -4676,19 +4682,19 @@
         <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4706,7 +4712,7 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -4723,10 +4729,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4752,16 +4758,16 @@
         <v>103</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4810,7 +4816,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4828,13 +4834,13 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4845,10 +4851,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4871,16 +4877,16 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4930,7 +4936,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4948,13 +4954,13 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -4965,10 +4971,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4994,14 +5000,14 @@
         <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5011,7 +5017,7 @@
         <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>79</v>
+        <v>254</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>79</v>
@@ -5050,7 +5056,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5068,16 +5074,16 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -5085,10 +5091,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5111,17 +5117,17 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5170,7 +5176,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5188,13 +5194,13 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -5205,10 +5211,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5231,19 +5237,19 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5292,7 +5298,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5310,13 +5316,13 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5327,10 +5333,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5353,19 +5359,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5414,7 +5420,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5432,13 +5438,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5449,14 +5455,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5475,17 +5481,17 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5510,13 +5516,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5534,7 +5540,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5549,16 +5555,16 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5569,10 +5575,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5595,13 +5601,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5652,7 +5658,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5670,7 +5676,7 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5687,10 +5693,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5719,7 +5725,7 @@
         <v>136</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>138</v>
@@ -5760,19 +5766,19 @@
         <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5790,7 +5796,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5807,10 +5813,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5833,19 +5839,19 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5894,7 +5900,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5912,16 +5918,16 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -5929,10 +5935,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5955,19 +5961,19 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -6016,7 +6022,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6034,31 +6040,31 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6077,13 +6083,13 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6134,7 +6140,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>89</v>
@@ -6149,19 +6155,19 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -6169,10 +6175,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6195,16 +6201,16 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6254,7 +6260,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6269,30 +6275,30 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6315,16 +6321,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6362,17 +6368,17 @@
         <v>79</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6381,22 +6387,22 @@
         <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6407,13 +6413,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>79</v>
@@ -6435,16 +6441,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6494,7 +6500,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6503,36 +6509,36 @@
         <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6555,13 +6561,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6612,7 +6618,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6630,10 +6636,10 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
@@ -6647,10 +6653,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6673,13 +6679,13 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6730,7 +6736,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6748,10 +6754,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6765,10 +6771,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6791,13 +6797,13 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6848,7 +6854,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6863,10 +6869,10 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
@@ -6883,10 +6889,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6909,13 +6915,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6966,7 +6972,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6984,7 +6990,7 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
@@ -7001,10 +7007,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7033,7 +7039,7 @@
         <v>136</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>138</v>
@@ -7086,7 +7092,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7104,7 +7110,7 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
@@ -7121,14 +7127,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7150,10 +7156,10 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>138</v>
@@ -7208,7 +7214,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7243,10 +7249,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7269,17 +7275,17 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7304,13 +7310,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7328,7 +7334,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7343,16 +7349,16 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7363,10 +7369,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7389,17 +7395,17 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7448,7 +7454,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>89</v>
@@ -7463,19 +7469,19 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -7483,10 +7489,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7509,17 +7515,17 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7568,7 +7574,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7586,7 +7592,7 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7603,10 +7609,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7629,17 +7635,17 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7688,7 +7694,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7706,10 +7712,10 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>79</v>
@@ -7723,10 +7729,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7749,16 +7755,16 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7784,13 +7790,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7808,7 +7814,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7823,19 +7829,19 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>79</v>
@@ -7843,10 +7849,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7869,16 +7875,16 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7928,7 +7934,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7943,13 +7949,13 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>79</v>
@@ -7963,10 +7969,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7989,16 +7995,16 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8024,13 +8030,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -8048,7 +8054,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8066,13 +8072,13 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8083,10 +8089,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8109,16 +8115,16 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8144,13 +8150,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -8168,7 +8174,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8186,7 +8192,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -8203,10 +8209,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8229,16 +8235,16 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8288,7 +8294,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8306,7 +8312,7 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -8323,10 +8329,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8349,16 +8355,16 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8384,13 +8390,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8408,7 +8414,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8426,7 +8432,7 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
@@ -8443,10 +8449,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8469,17 +8475,17 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8528,7 +8534,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8546,7 +8552,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8563,10 +8569,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8589,13 +8595,13 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8622,13 +8628,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8646,7 +8652,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8664,7 +8670,7 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8681,10 +8687,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8707,13 +8713,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8764,7 +8770,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8779,16 +8785,16 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8799,10 +8805,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8825,13 +8831,13 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8882,7 +8888,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8900,7 +8906,7 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
@@ -8917,10 +8923,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8949,7 +8955,7 @@
         <v>136</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>138</v>
@@ -8990,19 +8996,19 @@
         <v>79</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9020,7 +9026,7 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
@@ -9037,10 +9043,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9063,16 +9069,16 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9122,7 +9128,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9140,7 +9146,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -9157,10 +9163,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9183,13 +9189,13 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9240,7 +9246,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9258,7 +9264,7 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
@@ -9275,10 +9281,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9301,13 +9307,13 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9358,7 +9364,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>89</v>
@@ -9376,7 +9382,7 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -9385,18 +9391,18 @@
         <v>132</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9419,13 +9425,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9476,7 +9482,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9494,7 +9500,7 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -9511,10 +9517,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9537,13 +9543,13 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9594,7 +9600,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9612,7 +9618,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9629,10 +9635,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9661,7 +9667,7 @@
         <v>136</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>138</v>
@@ -9714,7 +9720,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9732,7 +9738,7 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
@@ -9749,14 +9755,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9778,10 +9784,10 @@
         <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>138</v>
@@ -9836,7 +9842,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9871,10 +9877,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9897,13 +9903,13 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9933,10 +9939,10 @@
         <v>113</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
@@ -9954,7 +9960,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9972,7 +9978,7 @@
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
@@ -9989,10 +9995,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10015,13 +10021,13 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10072,7 +10078,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>89</v>
@@ -10090,7 +10096,7 @@
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
@@ -10107,10 +10113,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10133,19 +10139,19 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -10194,7 +10200,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10212,7 +10218,7 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
@@ -10229,10 +10235,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10255,16 +10261,16 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10290,13 +10296,13 @@
         <v>79</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>79</v>
@@ -10314,7 +10320,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10332,7 +10338,7 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$59</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="465">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -667,6 +667,15 @@
     <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="371883000"/&gt;
+    &lt;display value="Outpatient procedure (procedure)"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>A code that classifies a procedure for searching, sorting and display purposes.</t>
   </si>
   <si>
@@ -679,7 +688,47 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>Procedure.category.id</t>
+    <t>1314: fixed value = http://snomed.info/sct#371883000 Outpatient procedure (procedure)</t>
+  </si>
+  <si>
+    <t>Procedure.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type
+</t>
+  </si>
+  <si>
+    <t>Identification of the procedure</t>
+  </si>
+  <si>
+    <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
+  </si>
+  <si>
+    <t>0..1 to account for primarily narrative only resources.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Codes describing the type of  Procedure</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-procedure-code</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>OBR-44/OBR-45</t>
+  </si>
+  <si>
+    <t>Procedure.code.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -698,7 +747,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Procedure.category.extension</t>
+    <t>Procedure.code.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -717,7 +766,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Procedure.category.coding</t>
+    <t>Procedure.code.coding</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
@@ -745,134 +794,10 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>Procedure.category.coding.id</t>
-  </si>
-  <si>
-    <t>Procedure.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Procedure.category.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Procedure.category.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Procedure.category.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>371883000</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>1314: fixed value = #371883000</t>
-  </si>
-  <si>
-    <t>Procedure.category.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Procedure.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>Procedure.category.text</t>
+    <t>1413: source value from V CPT - CPT &gt; CPT (#9000010.18-.01 &gt; 81-)</t>
+  </si>
+  <si>
+    <t>Procedure.code.text</t>
   </si>
   <si>
     <t>Plain text representation of the concept</t>
@@ -894,58 +819,6 @@
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>Procedure.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type
-</t>
-  </si>
-  <si>
-    <t>Identification of the procedure</t>
-  </si>
-  <si>
-    <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
-  </si>
-  <si>
-    <t>0..1 to account for primarily narrative only resources.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Codes describing the type of  Procedure</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-procedure-code</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>OBR-44/OBR-45</t>
-  </si>
-  <si>
-    <t>Procedure.code.id</t>
-  </si>
-  <si>
-    <t>Procedure.code.extension</t>
-  </si>
-  <si>
-    <t>Procedure.code.coding</t>
-  </si>
-  <si>
-    <t>1413: source value from V CPT - CPT &gt; CPT (#9000010.18-.01 &gt; 81-)</t>
-  </si>
-  <si>
-    <t>Procedure.code.text</t>
   </si>
   <si>
     <t>1301: source value from V CPT - PROVIDER NARRATIVE &gt; PROVIDER NARRATIVE - NARRATIVE (#9000010.18-.04 &gt; 9999999.27-.01)</t>
@@ -1921,7 +1794,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP70"/>
+  <dimension ref="A1:AP59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.296875" customWidth="true" bestFit="true"/>
@@ -4030,7 +3903,7 @@
         <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>79</v>
@@ -4057,7 +3930,7 @@
         <v>79</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>79</v>
@@ -4075,10 +3948,10 @@
         <v>200</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -4114,16 +3987,16 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>79</v>
@@ -4131,42 +4004,44 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+      <c r="O19" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
@@ -4190,13 +4065,13 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -4214,7 +4089,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4226,19 +4101,19 @@
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>79</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>79</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4249,21 +4124,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>79</v>
@@ -4275,17 +4150,15 @@
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4322,37 +4195,37 @@
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4369,14 +4242,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4392,23 +4265,21 @@
         <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
       </c>
@@ -4444,19 +4315,19 @@
         <v>79</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4468,7 +4339,7 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
@@ -4480,7 +4351,7 @@
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4491,10 +4362,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4505,28 +4376,32 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4574,34 +4449,34 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
@@ -4609,44 +4484,46 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>136</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
@@ -4682,71 +4559,71 @@
         <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>79</v>
+        <v>255</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>79</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>79</v>
+        <v>259</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>79</v>
@@ -4755,20 +4632,16 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4816,10 +4689,10 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>89</v>
@@ -4831,19 +4704,19 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>79</v>
@@ -4851,10 +4724,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4868,7 +4741,7 @@
         <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>79</v>
@@ -4877,16 +4750,16 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>213</v>
+        <v>269</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4936,7 +4809,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4951,30 +4824,30 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>79</v>
+        <v>277</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>79</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>279</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>279</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4997,18 +4870,18 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>109</v>
+        <v>280</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
       </c>
@@ -5017,7 +4890,7 @@
         <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>254</v>
+        <v>79</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>79</v>
@@ -5044,19 +4917,17 @@
         <v>79</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5065,25 +4936,25 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>79</v>
+        <v>287</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>258</v>
+        <v>79</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -5091,12 +4962,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>79</v>
       </c>
@@ -5108,7 +4981,7 @@
         <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>79</v>
@@ -5117,18 +4990,18 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>213</v>
+        <v>291</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
@@ -5176,7 +5049,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5185,36 +5058,36 @@
         <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>79</v>
+        <v>287</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>79</v>
+        <v>292</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5237,20 +5110,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
@@ -5298,7 +5167,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5316,13 +5185,13 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>274</v>
+        <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5333,10 +5202,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5359,20 +5228,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>213</v>
+        <v>295</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5420,7 +5285,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5438,13 +5303,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>79</v>
+        <v>304</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5455,24 +5320,24 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>79</v>
@@ -5481,18 +5346,16 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>196</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>287</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5516,13 +5379,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5540,13 +5403,13 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -5555,16 +5418,16 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>294</v>
+        <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5575,10 +5438,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5601,13 +5464,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5658,7 +5521,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5676,7 +5539,7 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5693,10 +5556,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5725,7 +5588,7 @@
         <v>136</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>138</v>
@@ -5766,19 +5629,19 @@
         <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5796,7 +5659,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5813,14 +5676,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5830,28 +5693,28 @@
         <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>226</v>
+        <v>315</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>227</v>
+        <v>316</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>229</v>
+        <v>144</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5900,7 +5763,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>230</v>
+        <v>317</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5912,22 +5775,22 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>231</v>
+        <v>132</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>298</v>
+        <v>79</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -5935,10 +5798,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5952,7 +5815,7 @@
         <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>79</v>
@@ -5961,19 +5824,17 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>276</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>279</v>
+        <v>321</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5998,13 +5859,13 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -6022,7 +5883,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6037,34 +5898,34 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>79</v>
+        <v>324</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>281</v>
+        <v>325</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>282</v>
+        <v>326</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>301</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>303</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6083,16 +5944,18 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
       </c>
@@ -6140,7 +6003,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>89</v>
@@ -6155,19 +6018,19 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -6175,10 +6038,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6192,27 +6055,27 @@
         <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6260,7 +6123,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6275,30 +6138,30 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>321</v>
+        <v>79</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>322</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6312,7 +6175,7 @@
         <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>79</v>
@@ -6321,18 +6184,18 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
       </c>
@@ -6368,17 +6231,19 @@
         <v>79</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AC37" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6387,22 +6252,22 @@
         <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>329</v>
+        <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>332</v>
+        <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6413,14 +6278,12 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6429,7 +6292,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>90</v>
@@ -6441,16 +6304,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>335</v>
+        <v>196</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6476,13 +6339,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6500,45 +6363,45 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>332</v>
+        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>337</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6549,7 +6412,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6561,15 +6424,17 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6618,13 +6483,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6633,13 +6498,13 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>79</v>
+        <v>365</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
@@ -6653,10 +6518,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6667,7 +6532,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
@@ -6679,15 +6544,17 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>339</v>
+        <v>196</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6712,13 +6579,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6736,13 +6603,13 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
@@ -6754,13 +6621,13 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6771,10 +6638,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6785,7 +6652,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6797,15 +6664,17 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>350</v>
+        <v>196</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -6830,13 +6699,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>79</v>
+        <v>379</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6854,13 +6723,13 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>79</v>
@@ -6869,10 +6738,10 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>353</v>
+        <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
@@ -6889,10 +6758,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6903,7 +6772,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
@@ -6915,15 +6784,17 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>213</v>
+        <v>382</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>214</v>
+        <v>383</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6972,25 +6843,25 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>216</v>
+        <v>381</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>217</v>
+        <v>386</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
@@ -7007,14 +6878,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7033,16 +6904,16 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>135</v>
+        <v>196</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>136</v>
+        <v>388</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>219</v>
+        <v>389</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>138</v>
+        <v>390</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7068,13 +6939,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -7092,7 +6963,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>223</v>
+        <v>387</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7104,13 +6975,13 @@
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>217</v>
+        <v>393</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
@@ -7127,14 +6998,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>358</v>
+        <v>79</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7147,25 +7018,23 @@
         <v>79</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>135</v>
+        <v>395</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>144</v>
+        <v>398</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7214,7 +7083,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7226,13 +7095,13 @@
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>132</v>
+        <v>393</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
@@ -7249,10 +7118,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>399</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7263,7 +7132,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7272,21 +7141,19 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>196</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>363</v>
+        <v>400</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>364</v>
+        <v>401</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>365</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
       </c>
@@ -7313,10 +7180,10 @@
         <v>200</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>366</v>
+        <v>402</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>367</v>
+        <v>403</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7334,13 +7201,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>399</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7349,16 +7216,16 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>368</v>
+        <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>369</v>
+        <v>404</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7369,10 +7236,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7380,33 +7247,31 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>375</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
       </c>
@@ -7454,13 +7319,13 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
@@ -7469,19 +7334,19 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>380</v>
+        <v>79</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -7489,10 +7354,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7515,18 +7380,16 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>382</v>
+        <v>227</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>383</v>
+        <v>228</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>384</v>
+        <v>229</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>385</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7574,7 +7437,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>381</v>
+        <v>230</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7586,13 +7449,13 @@
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>386</v>
+        <v>231</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7609,21 +7472,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>79</v>
@@ -7632,21 +7495,21 @@
         <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>388</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>389</v>
+        <v>136</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7682,40 +7545,40 @@
         <v>79</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>387</v>
+        <v>237</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>392</v>
+        <v>231</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>393</v>
+        <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>79</v>
@@ -7729,10 +7592,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7743,10 +7606,10 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>79</v>
@@ -7755,16 +7618,16 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>196</v>
+        <v>415</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7790,13 +7653,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>398</v>
+        <v>79</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>399</v>
+        <v>79</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7814,13 +7677,13 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>79</v>
@@ -7829,19 +7692,19 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>400</v>
+        <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>79</v>
@@ -7849,10 +7712,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7863,7 +7726,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7875,17 +7738,15 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>405</v>
+        <v>291</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7934,13 +7795,13 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
@@ -7949,16 +7810,16 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7969,10 +7830,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7980,13 +7841,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>79</v>
@@ -7995,17 +7856,15 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>196</v>
+        <v>427</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8030,13 +7889,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>414</v>
+        <v>79</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>415</v>
+        <v>79</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -8054,13 +7913,13 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
@@ -8072,27 +7931,27 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>417</v>
+        <v>132</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>79</v>
+        <v>433</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8103,7 +7962,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -8112,20 +7971,18 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>196</v>
+        <v>306</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8150,13 +8007,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>422</v>
+        <v>79</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>423</v>
+        <v>79</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -8174,13 +8031,13 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
@@ -8192,7 +8049,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -8209,10 +8066,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8223,7 +8080,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8235,17 +8092,15 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>426</v>
+        <v>227</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>427</v>
+        <v>228</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8294,25 +8149,25 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>425</v>
+        <v>230</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>430</v>
+        <v>231</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -8329,14 +8184,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8355,16 +8210,16 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>432</v>
+        <v>136</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>434</v>
+        <v>138</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8390,13 +8245,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>435</v>
+        <v>79</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>436</v>
+        <v>79</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8414,7 +8269,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>431</v>
+        <v>237</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8426,13 +8281,13 @@
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>437</v>
+        <v>231</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
@@ -8449,14 +8304,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8469,23 +8324,25 @@
         <v>79</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>439</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>440</v>
+        <v>315</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>442</v>
+        <v>144</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8534,7 +8391,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>438</v>
+        <v>317</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8546,13 +8403,13 @@
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>437</v>
+        <v>132</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8569,10 +8426,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8583,7 +8440,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8598,10 +8455,10 @@
         <v>196</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8628,13 +8485,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>200</v>
+        <v>113</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8652,13 +8509,13 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -8670,7 +8527,7 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8687,10 +8544,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8698,10 +8555,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8713,13 +8570,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8770,13 +8627,13 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
@@ -8785,16 +8642,16 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>453</v>
+        <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>455</v>
+        <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8805,10 +8662,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8819,7 +8676,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8831,16 +8688,20 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>213</v>
+        <v>453</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>214</v>
+        <v>454</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
       </c>
@@ -8888,25 +8749,25 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>216</v>
+        <v>452</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>217</v>
+        <v>458</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
@@ -8923,14 +8784,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8949,16 +8810,16 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>135</v>
+        <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>136</v>
+        <v>460</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>219</v>
+        <v>461</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>138</v>
+        <v>456</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8984,31 +8845,31 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>79</v>
+        <v>462</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>79</v>
+        <v>463</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>223</v>
+        <v>459</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9020,13 +8881,13 @@
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>217</v>
+        <v>464</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
@@ -9038,1323 +8899,11 @@
         <v>79</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP70" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP70">
+  <autoFilter ref="A1:AP59">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10364,7 +8913,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI58">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -890,12 +890,7 @@
     <t>1300: reference from V CPT - VISIT (#9000010.18-.03)</t>
   </si>
   <si>
-    <t>Outpat.VProcedure.VisitDateTime
-Outpat.VProcedureCPTModifier.VisitDateTime
-Outpat.VProcedureDiagnosis.VisitDateTime
-Outpat.WorkloadVProcedure.VisitDateTime
-Outpat.WorkloadVProcedureCPTModifier.VisitDateTime
-Outpat.WorkloadVProcedureDiagnosis.VisitDateTime</t>
+    <t>Outpat.VProcedure.VisitDateTime,Outpat.VProcedureCPTModifier.VisitDateTime,Outpat.VProcedureDiagnosis.VisitDateTime,Outpat.WorkloadVProcedure.VisitDateTime,Outpat.WorkloadVProcedureCPTModifier.VisitDateTime,Outpat.WorkloadVProcedureDiagnosis.VisitDateTime</t>
   </si>
   <si>
     <t>Procedure.performed[x]</t>
@@ -943,10 +938,7 @@
     <t>1310: source value from V CPT - EVENT DATE AND TIME (#9000010.18-1201)</t>
   </si>
   <si>
-    <t>Outpat.VProcedure.EventDateTime
-Outpat.VProcedureDiagnosis.EventDateTime
-Outpat.WorkloadVProcedure.EventDateTime
-Outpat.WorkloadVProcedureDiagnosis.EventDateTime</t>
+    <t>Outpat.VProcedure.EventDateTime,Outpat.VProcedureDiagnosis.EventDateTime,Outpat.WorkloadVProcedure.EventDateTime,Outpat.WorkloadVProcedureDiagnosis.EventDateTime</t>
   </si>
   <si>
     <t>Procedure.recorder</t>
@@ -1380,8 +1372,7 @@
     <t>1312: source value from V CPT - COMMENTS (#9000010.18-81101)</t>
   </si>
   <si>
-    <t>Outpat.VProcedure.Comments
-Outpat.WorkloadVProcedure.Comments</t>
+    <t>Outpat.VProcedure.Comments,Outpat.WorkloadVProcedure.Comments</t>
   </si>
   <si>
     <t>Procedure.focalDevice</t>
@@ -1837,7 +1828,7 @@
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="122.95703125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="51.578125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -247,12 +253,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -611,6 +611,9 @@
 </t>
   </si>
   <si>
+    <t>1539: fixed value = #completed</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -618,9 +621,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1539: fixed value = #completed</t>
   </si>
   <si>
     <t>Procedure.statusReason</t>
@@ -682,13 +682,13 @@
     <t>http://hl7.org/fhir/ValueSet/procedure-category</t>
   </si>
   <si>
+    <t>1314: fixed value = http://snomed.info/sct#371883000 Outpatient procedure (procedure)</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>1314: fixed value = http://snomed.info/sct#371883000 Outpatient procedure (procedure)</t>
   </si>
   <si>
     <t>Procedure.code</t>
@@ -788,15 +788,15 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
+    <t>1413: source value from V CPT - CPT &gt; CPT (#9000010.18-.01 &gt; 81-)</t>
+  </si>
+  <si>
     <t>union(., ./translation)</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>1413: source value from V CPT - CPT &gt; CPT (#9000010.18-.01 &gt; 81-)</t>
-  </si>
-  <si>
     <t>Procedure.code.text</t>
   </si>
   <si>
@@ -815,16 +815,16 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>1301: source value from V CPT - PROVIDER NARRATIVE &gt; PROVIDER NARRATIVE - NARRATIVE (#9000010.18-.04 &gt; 9999999.27-.01)</t>
+  </si>
+  <si>
+    <t>Dim.ProviderNarrative.ProviderNarrative</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>1301: source value from V CPT - PROVIDER NARRATIVE &gt; PROVIDER NARRATIVE - NARRATIVE (#9000010.18-.04 &gt; 9999999.27-.01)</t>
-  </si>
-  <si>
-    <t>Dim.ProviderNarrative.ProviderNarrative</t>
   </si>
   <si>
     <t>Procedure.subject</t>
@@ -844,6 +844,9 @@
     <t>The person, animal or group on which the procedure was performed.</t>
   </si>
   <si>
+    <t>1299: reference from V CPT - PATIENT NAME &gt; PATIENT/IHS - NAME (#9000010.18-.02 &gt; 9000001-.01)</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -854,9 +857,6 @@
   </si>
   <si>
     <t>PID-3</t>
-  </si>
-  <si>
-    <t>1299: reference from V CPT - PATIENT NAME &gt; PATIENT/IHS - NAME (#9000010.18-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Procedure.encounter</t>
@@ -875,6 +875,12 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
   </si>
   <si>
+    <t>1300: reference from V CPT - VISIT (#9000010.18-.03)</t>
+  </si>
+  <si>
+    <t>Outpat.VProcedure.VisitDateTime,Outpat.VProcedureCPTModifier.VisitDateTime,Outpat.VProcedureDiagnosis.VisitDateTime,Outpat.WorkloadVProcedure.VisitDateTime,Outpat.WorkloadVProcedureCPTModifier.VisitDateTime,Outpat.WorkloadVProcedureDiagnosis.VisitDateTime</t>
+  </si>
+  <si>
     <t>Event.context</t>
   </si>
   <si>
@@ -885,12 +891,6 @@
   </si>
   <si>
     <t>PV1-19</t>
-  </si>
-  <si>
-    <t>1300: reference from V CPT - VISIT (#9000010.18-.03)</t>
-  </si>
-  <si>
-    <t>Outpat.VProcedure.VisitDateTime,Outpat.VProcedureCPTModifier.VisitDateTime,Outpat.VProcedureDiagnosis.VisitDateTime,Outpat.WorkloadVProcedure.VisitDateTime,Outpat.WorkloadVProcedureCPTModifier.VisitDateTime,Outpat.WorkloadVProcedureDiagnosis.VisitDateTime</t>
   </si>
   <si>
     <t>Procedure.performed[x]</t>
@@ -1060,6 +1060,9 @@
     <t>A reference to Device supports use cases, such as pacemakers.</t>
   </si>
   <si>
+    <t>1311: reference from V CPT - ENCOUNTER PROVIDER (#9000010.18-1204)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1070,9 +1073,6 @@
   </si>
   <si>
     <t>ORC-19/PRT-5</t>
-  </si>
-  <si>
-    <t>1311: reference from V CPT - ENCOUNTER PROVIDER (#9000010.18-1204)</t>
   </si>
   <si>
     <t>Procedure.performer.onBehalfOf</t>
@@ -1134,6 +1134,9 @@
     <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
   </si>
   <si>
+    <t>1309: source value from V CPT - DIAGNOSIS 8 &gt; ICD DIAGNOSIS (#9000010.18-.15 &gt; 80-)</t>
+  </si>
+  <si>
     <t>Event.reasonCode</t>
   </si>
   <si>
@@ -1141,9 +1144,6 @@
   </si>
   <si>
     <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>1309: source value from V CPT - DIAGNOSIS 8 &gt; ICD DIAGNOSIS (#9000010.18-.15 &gt; 80-)</t>
   </si>
   <si>
     <t>Procedure.reasonReference</t>
@@ -1366,13 +1366,13 @@
     <t>Annotation.text</t>
   </si>
   <si>
+    <t>1312: source value from V CPT - COMMENTS (#9000010.18-81101)</t>
+  </si>
+  <si>
+    <t>Outpat.VProcedure.Comments,Outpat.WorkloadVProcedure.Comments</t>
+  </si>
+  <si>
     <t>Act.text</t>
-  </si>
-  <si>
-    <t>1312: source value from V CPT - COMMENTS (#9000010.18-81101)</t>
-  </si>
-  <si>
-    <t>Outpat.VProcedure.Comments,Outpat.WorkloadVProcedure.Comments</t>
   </si>
   <si>
     <t>Procedure.focalDevice</t>
@@ -1823,12 +1823,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="142.56640625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="122.95703125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="122.95703125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="142.56640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="105.16015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2061,16 +2061,16 @@
         <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>79</v>
@@ -2662,13 +2662,13 @@
         <v>79</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>79</v>
@@ -2782,13 +2782,13 @@
         <v>79</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>79</v>
@@ -2902,13 +2902,13 @@
         <v>79</v>
       </c>
       <c r="AL9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>79</v>
@@ -3024,13 +3024,13 @@
         <v>79</v>
       </c>
       <c r="AL10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN10" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>79</v>
@@ -3143,22 +3143,22 @@
         <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3261,16 +3261,16 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>79</v>
@@ -3381,16 +3381,16 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3499,16 +3499,16 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3619,16 +3619,16 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3740,13 +3740,13 @@
         <v>190</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>193</v>
@@ -3857,16 +3857,16 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3975,16 +3975,16 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>213</v>
@@ -4095,22 +4095,22 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -4216,13 +4216,13 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4336,13 +4336,13 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4455,10 +4455,10 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>79</v>
+        <v>245</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
@@ -4467,10 +4467,10 @@
         <v>246</v>
       </c>
       <c r="AO22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP22" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4577,19 +4577,19 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>79</v>
+        <v>254</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>256</v>
+        <v>79</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>257</v>
@@ -4698,19 +4698,19 @@
         <v>263</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4933,22 +4933,22 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5055,22 +5055,22 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5176,16 +5176,16 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5294,16 +5294,16 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5409,16 +5409,16 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5530,13 +5530,13 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5650,13 +5650,13 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5772,13 +5772,13 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5889,22 +5889,22 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AM34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -6012,19 +6012,19 @@
         <v>332</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6132,13 +6132,13 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6252,16 +6252,16 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6372,13 +6372,13 @@
         <v>356</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>359</v>
@@ -6489,19 +6489,19 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AN39" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AO39" t="s" s="2">
-        <v>79</v>
+        <v>359</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6612,19 +6612,19 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -6732,13 +6732,13 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6852,13 +6852,13 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6972,13 +6972,13 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -7092,13 +7092,13 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7210,13 +7210,13 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7325,22 +7325,22 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7446,13 +7446,13 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7566,13 +7566,13 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7686,19 +7686,19 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7804,19 +7804,19 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AM50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -7919,22 +7919,22 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>79</v>
+        <v>431</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>433</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -8040,13 +8040,13 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8158,13 +8158,13 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8278,13 +8278,13 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8400,13 +8400,13 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8518,13 +8518,13 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8636,13 +8636,13 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8758,13 +8758,13 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8878,13 +8878,13 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file V CPT (#9000010.18) to us-core-procedure</t>
+    <t>This StructureDefinition contains the maps for VistA file V CPT (9000010.18) to us-core-procedure</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -788,7 +788,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1413: source value from V CPT - CPT &gt; CPT (#9000010.18-.01 &gt; 81-)</t>
+    <t>1413: source value from V CPT - CPT &gt; CPT (9000010.18-.01 &gt; 81-)</t>
   </si>
   <si>
     <t>union(., ./translation)</t>
@@ -815,7 +815,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1301: source value from V CPT - PROVIDER NARRATIVE &gt; PROVIDER NARRATIVE - NARRATIVE (#9000010.18-.04 &gt; 9999999.27-.01)</t>
+    <t>1301: source value from V CPT - PROVIDER NARRATIVE &gt; PROVIDER NARRATIVE - NARRATIVE (9000010.18-.04 &gt; 9999999.27-.01)</t>
   </si>
   <si>
     <t>Dim.ProviderNarrative.ProviderNarrative</t>
@@ -844,7 +844,7 @@
     <t>The person, animal or group on which the procedure was performed.</t>
   </si>
   <si>
-    <t>1299: reference from V CPT - PATIENT NAME &gt; PATIENT/IHS - NAME (#9000010.18-.02 &gt; 9000001-.01)</t>
+    <t>1299: reference from V CPT - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.18-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -875,7 +875,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
   </si>
   <si>
-    <t>1300: reference from V CPT - VISIT (#9000010.18-.03)</t>
+    <t>1300: reference from V CPT - VISIT (9000010.18-.03)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.VisitDateTime,Outpat.VProcedureCPTModifier.VisitDateTime,Outpat.VProcedureDiagnosis.VisitDateTime,Outpat.WorkloadVProcedure.VisitDateTime,Outpat.WorkloadVProcedureCPTModifier.VisitDateTime,Outpat.WorkloadVProcedureDiagnosis.VisitDateTime</t>
@@ -935,7 +935,7 @@
 </t>
   </si>
   <si>
-    <t>1310: source value from V CPT - EVENT DATE AND TIME (#9000010.18-1201)</t>
+    <t>1310: source value from V CPT - EVENT DATE AND TIME (9000010.18-1201)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.EventDateTime,Outpat.VProcedureDiagnosis.EventDateTime,Outpat.WorkloadVProcedure.EventDateTime,Outpat.WorkloadVProcedureDiagnosis.EventDateTime</t>
@@ -1060,7 +1060,7 @@
     <t>A reference to Device supports use cases, such as pacemakers.</t>
   </si>
   <si>
-    <t>1311: reference from V CPT - ENCOUNTER PROVIDER (#9000010.18-1204)</t>
+    <t>1311: reference from V CPT - ENCOUNTER PROVIDER (9000010.18-1204)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1134,7 +1134,7 @@
     <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
   </si>
   <si>
-    <t>1309: source value from V CPT - DIAGNOSIS 8 &gt; ICD DIAGNOSIS (#9000010.18-.15 &gt; 80-)</t>
+    <t>1309: source value from V CPT - DIAGNOSIS 8 &gt; ICD DIAGNOSIS (9000010.18-.15 &gt; 80-)</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1366,7 +1366,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1312: source value from V CPT - COMMENTS (#9000010.18-81101)</t>
+    <t>1312: source value from V CPT - COMMENTS (9000010.18-81101)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.Comments,Outpat.WorkloadVProcedure.Comments</t>
@@ -1823,7 +1823,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="122.95703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="121.41796875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="142.56640625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="469">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -791,6 +791,9 @@
     <t>1413: source value from V CPT - CPT &gt; CPT (9000010.18-.01 &gt; 81-)</t>
   </si>
   <si>
+    <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN</t>
+  </si>
+  <si>
     <t>union(., ./translation)</t>
   </si>
   <si>
@@ -818,7 +821,8 @@
     <t>1301: source value from V CPT - PROVIDER NARRATIVE &gt; PROVIDER NARRATIVE - NARRATIVE (9000010.18-.04 &gt; 9999999.27-.01)</t>
   </si>
   <si>
-    <t>Dim.ProviderNarrative.ProviderNarrative</t>
+    <t>Outpat.VProcedure.ProviderNarrativeIEN,Outpat.WorkloadVProcedure.ProviderNarrativeIEN
+Dim.ProviderNarrative.ProviderNarrative</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -847,6 +851,9 @@
     <t>1299: reference from V CPT - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.18-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
+    <t>Outpat.VProcedure.PatientIEN,Outpat.VProcedureCPTModifier.PatientIEN,Outpat.VProcedureDiagnosis.PatientIEN,Outpat.WorkloadVProcedure.PatientIEN,Outpat.WorkloadVProcedureCPTModifier.PatientIEN,Outpat.WorkloadVProcedureDiagnosis.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -878,7 +885,7 @@
     <t>1300: reference from V CPT - VISIT (9000010.18-.03)</t>
   </si>
   <si>
-    <t>Outpat.VProcedure.VisitDateTime,Outpat.VProcedureCPTModifier.VisitDateTime,Outpat.VProcedureDiagnosis.VisitDateTime,Outpat.WorkloadVProcedure.VisitDateTime,Outpat.WorkloadVProcedureCPTModifier.VisitDateTime,Outpat.WorkloadVProcedureDiagnosis.VisitDateTime</t>
+    <t>Outpat.VProcedure.VisitDateTime,Outpat.VProcedure.VisitIEN,Outpat.VProcedureCPTModifier.VisitDateTime,Outpat.VProcedureCPTModifier.VisitIEN,Outpat.VProcedureDiagnosis.VisitDateTime,Outpat.VProcedureDiagnosis.VisitIEN,Outpat.WorkloadVProcedure.VisitDateTime,Outpat.WorkloadVProcedure.VisitIEN,Outpat.WorkloadVProcedureCPTModifier.VisitDateTime,Outpat.WorkloadVProcedureCPTModifier.VisitIEN,Outpat.WorkloadVProcedureDiagnosis.VisitDateTime,Outpat.WorkloadVProcedureDiagnosis.VisitIEN</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1063,6 +1070,9 @@
     <t>1311: reference from V CPT - ENCOUNTER PROVIDER (9000010.18-1204)</t>
   </si>
   <si>
+    <t>Outpat.VProcedure.EncounterProviderIEN,Outpat.WorkloadVProcedure.EncounterProviderIEN</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1135,6 +1145,9 @@
   </si>
   <si>
     <t>1309: source value from V CPT - DIAGNOSIS 8 &gt; ICD DIAGNOSIS (9000010.18-.15 &gt; 80-)</t>
+  </si>
+  <si>
+    <t>Outpat.VProcedureDiagnosis.ICDIEN,Outpat.WorkloadVProcedureDiagnosis.ICDIEN</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -4458,27 +4471,27 @@
         <v>245</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4504,16 +4517,16 @@
         <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -4562,7 +4575,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4577,34 +4590,34 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4623,13 +4636,13 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4680,7 +4693,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>89</v>
@@ -4695,30 +4708,30 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4741,16 +4754,16 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4800,7 +4813,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4815,30 +4828,30 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4861,16 +4874,16 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4908,7 +4921,7 @@
         <v>79</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -4918,7 +4931,7 @@
         <v>236</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4939,27 +4952,27 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>79</v>
@@ -4981,16 +4994,16 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5040,7 +5053,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5055,30 +5068,30 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5101,13 +5114,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5158,7 +5171,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5182,10 +5195,10 @@
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5193,10 +5206,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5219,13 +5232,13 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5276,7 +5289,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5300,10 +5313,10 @@
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5311,10 +5324,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5337,13 +5350,13 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5394,7 +5407,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5415,10 +5428,10 @@
         <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5429,10 +5442,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5547,10 +5560,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5667,14 +5680,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5696,10 +5709,10 @@
         <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>138</v>
@@ -5754,7 +5767,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5789,10 +5802,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5818,14 +5831,14 @@
         <v>196</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5853,10 +5866,10 @@
         <v>200</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -5874,7 +5887,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5895,24 +5908,24 @@
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5935,17 +5948,17 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -5994,7 +6007,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>89</v>
@@ -6009,30 +6022,30 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6055,17 +6068,17 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6114,7 +6127,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6138,7 +6151,7 @@
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6149,10 +6162,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6175,17 +6188,17 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6234,7 +6247,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6258,10 +6271,10 @@
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6269,10 +6282,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6298,13 +6311,13 @@
         <v>196</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6333,10 +6346,10 @@
         <v>200</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6354,7 +6367,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6369,19 +6382,19 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -6389,10 +6402,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6415,16 +6428,16 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6474,7 +6487,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6495,13 +6508,13 @@
         <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6509,10 +6522,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6538,13 +6551,13 @@
         <v>196</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6573,28 +6586,28 @@
         <v>200</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6618,21 +6631,21 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6658,13 +6671,13 @@
         <v>196</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6693,28 +6706,28 @@
         <v>200</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6738,7 +6751,7 @@
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6749,10 +6762,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6775,16 +6788,16 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6834,7 +6847,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6858,7 +6871,7 @@
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6869,10 +6882,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6898,13 +6911,13 @@
         <v>196</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6933,28 +6946,28 @@
         <v>200</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6978,7 +6991,7 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -6989,10 +7002,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7015,17 +7028,17 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7074,7 +7087,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7098,7 +7111,7 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7109,10 +7122,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7138,10 +7151,10 @@
         <v>196</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7171,28 +7184,28 @@
         <v>200</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="Z45" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7216,7 +7229,7 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7227,10 +7240,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7253,13 +7266,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7310,7 +7323,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7331,24 +7344,24 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7463,10 +7476,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7583,10 +7596,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7609,16 +7622,16 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7668,7 +7681,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7692,7 +7705,7 @@
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7703,10 +7716,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7729,13 +7742,13 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7786,7 +7799,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7810,7 +7823,7 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7821,10 +7834,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7847,13 +7860,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7904,7 +7917,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>89</v>
@@ -7919,16 +7932,16 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7939,10 +7952,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7965,13 +7978,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8022,7 +8035,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8046,7 +8059,7 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8057,10 +8070,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8175,10 +8188,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8295,14 +8308,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8324,10 +8337,10 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>138</v>
@@ -8382,7 +8395,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8417,10 +8430,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8446,10 +8459,10 @@
         <v>196</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8479,28 +8492,28 @@
         <v>113</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="Z56" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8524,7 +8537,7 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8535,10 +8548,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8561,13 +8574,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8618,7 +8631,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>89</v>
@@ -8642,7 +8655,7 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8653,10 +8666,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8679,19 +8692,19 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -8740,7 +8753,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8764,7 +8777,7 @@
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8775,10 +8788,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8804,13 +8817,13 @@
         <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8839,28 +8852,28 @@
         <v>200</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="Z59" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8884,7 +8897,7 @@
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$77</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2957" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -800,6 +800,147 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
+    <t>Procedure.code.coding.id</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://www.ama-assn.org/go/cpt</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1413-3: fixed value = http://www.ama-assn.org/go/cpt</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>1413-1: source value from V CPT - CPT &gt; CPT - CPT CODE (9000010.18-.01 &gt; 81-.01)</t>
+  </si>
+  <si>
+    <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN
+Dim.CPT.CPTCode,Dim.CPT.CPTCode</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>1413-2: source value from V CPT - CPT &gt; CPT - SHORT NAME (9000010.18-.01 &gt; 81-2)</t>
+  </si>
+  <si>
+    <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN
+Dim.CPT.CPTName,Dim.CPT.CPTName</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
     <t>Procedure.code.text</t>
   </si>
   <si>
@@ -1157,6 +1298,48 @@
   </si>
   <si>
     <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>Procedure.reasonCode.id</t>
+  </si>
+  <si>
+    <t>Procedure.reasonCode.extension</t>
+  </si>
+  <si>
+    <t>Procedure.reasonCode.coding</t>
+  </si>
+  <si>
+    <t>Procedure.reasonCode.coding.id</t>
+  </si>
+  <si>
+    <t>Procedure.reasonCode.coding.extension</t>
+  </si>
+  <si>
+    <t>Procedure.reasonCode.coding.system</t>
+  </si>
+  <si>
+    <t>1309-1: undefined</t>
+  </si>
+  <si>
+    <t>Procedure.reasonCode.coding.version</t>
+  </si>
+  <si>
+    <t>Procedure.reasonCode.coding.code</t>
+  </si>
+  <si>
+    <t>1309-2: source value from V CPT - DIAGNOSIS 8 &gt; ICD DIAGNOSIS - CODE NUMBER (9000010.18-.15 &gt; 80-.01)</t>
+  </si>
+  <si>
+    <t>Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
+  </si>
+  <si>
+    <t>Procedure.reasonCode.coding.display</t>
+  </si>
+  <si>
+    <t>Procedure.reasonCode.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Procedure.reasonCode.text</t>
   </si>
   <si>
     <t>Procedure.reasonReference</t>
@@ -1798,11 +1981,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP59"/>
+  <dimension ref="A1:AP77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.12890625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.61328125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -4505,29 +4688,25 @@
         <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
@@ -4575,7 +4754,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4587,64 +4766,66 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>255</v>
+        <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>256</v>
+        <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>258</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>260</v>
+        <v>134</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>261</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>262</v>
+        <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4681,57 +4862,57 @@
         <v>79</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>265</v>
+        <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>266</v>
+        <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>268</v>
+        <v>79</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4754,18 +4935,20 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>271</v>
+        <v>103</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4774,7 +4957,7 @@
         <v>79</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>79</v>
@@ -4813,7 +4996,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4828,30 +5011,30 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>276</v>
+        <v>79</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4865,7 +5048,7 @@
         <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>79</v>
@@ -4874,16 +5057,16 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>282</v>
+        <v>227</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4921,17 +5104,19 @@
         <v>79</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4940,7 +5125,7 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>101</v>
@@ -4952,28 +5137,26 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>290</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>79</v>
       </c>
@@ -4994,18 +5177,18 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>293</v>
+        <v>109</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
@@ -5053,7 +5236,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5062,36 +5245,36 @@
         <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>290</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5105,7 +5288,7 @@
         <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>79</v>
@@ -5114,16 +5297,18 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>297</v>
+        <v>227</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
@@ -5171,7 +5356,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5186,30 +5371,30 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>301</v>
+        <v>79</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5232,16 +5417,20 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5289,7 +5478,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5313,21 +5502,21 @@
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5338,10 +5527,10 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>79</v>
@@ -5350,16 +5539,20 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>227</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5407,13 +5600,13 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -5422,59 +5615,59 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>79</v>
+        <v>302</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>311</v>
+        <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>79</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>227</v>
+        <v>307</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>228</v>
+        <v>308</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>229</v>
+        <v>309</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5525,10 +5718,10 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>230</v>
+        <v>305</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>89</v>
@@ -5537,65 +5730,65 @@
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>231</v>
+        <v>313</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>79</v>
+        <v>315</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>317</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>136</v>
+        <v>318</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>138</v>
+        <v>320</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5645,81 +5838,79 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>237</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>321</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>231</v>
+        <v>324</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>79</v>
+        <v>325</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>79</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>135</v>
+        <v>328</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
       </c>
@@ -5755,31 +5946,29 @@
         <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
@@ -5788,26 +5977,28 @@
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>79</v>
+        <v>333</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>132</v>
+        <v>334</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5819,7 +6010,7 @@
         <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>79</v>
@@ -5828,18 +6019,18 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>196</v>
+        <v>339</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5863,13 +6054,13 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>324</v>
+        <v>79</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -5887,7 +6078,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5896,36 +6087,36 @@
         <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>79</v>
+        <v>340</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5933,13 +6124,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>79</v>
@@ -5948,18 +6139,16 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>333</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
       </c>
@@ -6007,10 +6196,10 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>89</v>
@@ -6022,30 +6211,30 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>334</v>
+        <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>335</v>
+        <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>339</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6065,21 +6254,19 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>344</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6127,7 +6314,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6151,10 +6338,10 @@
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -6162,10 +6349,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6176,7 +6363,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -6188,18 +6375,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>350</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
       </c>
@@ -6247,13 +6432,13 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
@@ -6268,13 +6453,13 @@
         <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>79</v>
+        <v>357</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>352</v>
+        <v>79</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6282,10 +6467,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6296,29 +6481,27 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>354</v>
+        <v>228</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6343,13 +6526,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>357</v>
+        <v>79</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>358</v>
+        <v>79</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6367,34 +6550,34 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>230</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>359</v>
+        <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>360</v>
+        <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>361</v>
+        <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>362</v>
+        <v>231</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -6402,14 +6585,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6425,19 +6608,19 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>365</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>136</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
+        <v>233</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>368</v>
+        <v>138</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6487,7 +6670,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>364</v>
+        <v>237</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6499,7 +6682,7 @@
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
@@ -6508,13 +6691,13 @@
         <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>369</v>
+        <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>362</v>
+        <v>231</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6522,14 +6705,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>79</v>
+        <v>362</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6542,24 +6725,26 @@
         <v>79</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6583,13 +6768,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>374</v>
+        <v>79</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>375</v>
+        <v>79</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6607,7 +6792,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6619,7 +6804,7 @@
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
@@ -6631,21 +6816,21 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>376</v>
+        <v>132</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>377</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6671,15 +6856,15 @@
         <v>196</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6706,10 +6891,10 @@
         <v>200</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6727,7 +6912,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6748,24 +6933,24 @@
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>79</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6773,33 +6958,33 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6847,13 +7032,13 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
@@ -6862,30 +7047,30 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>79</v>
+        <v>380</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>79</v>
+        <v>385</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6896,7 +7081,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>79</v>
@@ -6908,18 +7093,18 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>196</v>
+        <v>387</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6943,13 +7128,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6967,13 +7152,13 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>79</v>
@@ -6991,7 +7176,7 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -7002,10 +7187,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7016,7 +7201,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -7025,20 +7210,20 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7087,13 +7272,13 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
@@ -7114,7 +7299,7 @@
         <v>397</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>79</v>
+        <v>398</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7122,10 +7307,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7139,24 +7324,26 @@
         <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>196</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7184,10 +7371,10 @@
         <v>200</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7205,7 +7392,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7220,19 +7407,19 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>79</v>
+        <v>405</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>79</v>
+        <v>406</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>79</v>
+        <v>407</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>408</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -7240,10 +7427,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7254,7 +7441,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7266,13 +7453,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>410</v>
+        <v>227</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>411</v>
+        <v>228</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>412</v>
+        <v>229</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7323,19 +7510,19 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>409</v>
+        <v>230</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
@@ -7344,35 +7531,35 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>414</v>
+        <v>231</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>415</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7384,15 +7571,17 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>228</v>
+        <v>136</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7429,31 +7618,31 @@
         <v>79</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
@@ -7476,14 +7665,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7499,21 +7688,23 @@
         <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>135</v>
+        <v>239</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7549,19 +7740,19 @@
         <v>79</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7573,7 +7764,7 @@
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
@@ -7585,21 +7776,21 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>79</v>
+        <v>248</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7619,20 +7810,18 @@
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>419</v>
+        <v>227</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>420</v>
+        <v>228</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7681,7 +7870,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>423</v>
+        <v>230</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7693,7 +7882,7 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
@@ -7705,32 +7894,32 @@
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>424</v>
+        <v>231</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7739,18 +7928,20 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>293</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>426</v>
+        <v>136</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7787,31 +7978,31 @@
         <v>79</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>428</v>
+        <v>237</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
@@ -7823,21 +8014,21 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>429</v>
+        <v>231</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7845,7 +8036,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>89</v>
@@ -7860,16 +8051,20 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>431</v>
+        <v>103</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>432</v>
+        <v>252</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7917,10 +8112,10 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>434</v>
+        <v>257</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>89</v>
@@ -7932,30 +8127,30 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>436</v>
+        <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>437</v>
+        <v>259</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>132</v>
+        <v>260</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7966,7 +8161,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -7975,18 +8170,20 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>308</v>
+        <v>227</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>439</v>
+        <v>262</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8035,13 +8232,13 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>438</v>
+        <v>265</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
@@ -8059,21 +8256,21 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>441</v>
+        <v>266</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>79</v>
+        <v>267</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8087,25 +8284,27 @@
         <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>227</v>
+        <v>109</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
       </c>
@@ -8153,7 +8352,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8165,44 +8364,44 @@
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>79</v>
+        <v>419</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>79</v>
+        <v>420</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>79</v>
+        <v>276</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
@@ -8211,21 +8410,21 @@
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>136</v>
+        <v>278</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8273,19 +8472,19 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
@@ -8297,56 +8496,56 @@
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>231</v>
+        <v>284</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>135</v>
+        <v>287</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>317</v>
+        <v>288</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>138</v>
+        <v>290</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>144</v>
+        <v>291</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8395,19 +8594,19 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>319</v>
+        <v>292</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
@@ -8419,21 +8618,21 @@
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>132</v>
+        <v>293</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8453,19 +8652,23 @@
         <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>446</v>
+        <v>296</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8489,13 +8692,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>448</v>
+        <v>79</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>449</v>
+        <v>79</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8513,7 +8716,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>445</v>
+        <v>300</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8537,21 +8740,21 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>450</v>
+        <v>303</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>79</v>
+        <v>304</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8559,10 +8762,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8571,18 +8774,20 @@
         <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>453</v>
+        <v>426</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8631,13 +8836,13 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
@@ -8652,13 +8857,13 @@
         <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>455</v>
+        <v>408</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>79</v>
@@ -8666,10 +8871,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8689,23 +8894,21 @@
         <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>457</v>
+        <v>196</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
       </c>
@@ -8729,13 +8932,13 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>79</v>
+        <v>434</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>79</v>
+        <v>435</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -8753,7 +8956,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8777,21 +8980,21 @@
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>79</v>
+        <v>437</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8802,7 +9005,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -8811,19 +9014,19 @@
         <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8852,10 +9055,10 @@
         <v>200</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -8873,13 +9076,13 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>79</v>
@@ -8897,17 +9100,2163 @@
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AO59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP59" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP59">
+  <autoFilter ref="A1:AP77">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8917,7 +11266,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI58">
+  <conditionalFormatting sqref="A2:AI76">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2957" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2957" uniqueCount="530">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1318,7 +1318,10 @@
     <t>Procedure.reasonCode.coding.system</t>
   </si>
   <si>
-    <t>1309-1: undefined</t>
+    <t>urn:see-termmap-in-mapParameter</t>
+  </si>
+  <si>
+    <t>1309-1: fixed value = urn:see-termmap-in-mapParameter</t>
   </si>
   <si>
     <t>Procedure.reasonCode.coding.version</t>
@@ -8073,7 +8076,7 @@
         <v>79</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>79</v>
@@ -8127,7 +8130,7 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>79</v>
@@ -8147,10 +8150,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8267,10 +8270,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8367,10 +8370,10 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -8387,10 +8390,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8507,10 +8510,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8629,10 +8632,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8751,10 +8754,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8777,16 +8780,16 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8836,7 +8839,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8857,7 +8860,7 @@
         <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>408</v>
@@ -8871,10 +8874,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8900,13 +8903,13 @@
         <v>196</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8935,10 +8938,10 @@
         <v>200</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -8956,7 +8959,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8980,21 +8983,21 @@
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9020,13 +9023,13 @@
         <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9055,10 +9058,10 @@
         <v>200</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -9076,7 +9079,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9100,7 +9103,7 @@
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -9111,10 +9114,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9137,16 +9140,16 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9196,7 +9199,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9220,7 +9223,7 @@
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9231,10 +9234,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9260,13 +9263,13 @@
         <v>196</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9295,10 +9298,10 @@
         <v>200</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>79</v>
@@ -9316,7 +9319,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9340,7 +9343,7 @@
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9351,10 +9354,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9377,17 +9380,17 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -9436,7 +9439,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9460,7 +9463,7 @@
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9471,10 +9474,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9500,10 +9503,10 @@
         <v>196</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9533,10 +9536,10 @@
         <v>200</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>79</v>
@@ -9554,7 +9557,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9578,7 +9581,7 @@
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9589,10 +9592,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9615,13 +9618,13 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9672,7 +9675,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9693,24 +9696,24 @@
         <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9825,10 +9828,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9945,10 +9948,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9971,16 +9974,16 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10030,7 +10033,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10054,7 +10057,7 @@
         <v>79</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>79</v>
@@ -10065,10 +10068,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10094,10 +10097,10 @@
         <v>339</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10148,7 +10151,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10172,7 +10175,7 @@
         <v>79</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>79</v>
@@ -10183,10 +10186,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10209,13 +10212,13 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10266,7 +10269,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>89</v>
@@ -10281,16 +10284,16 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10301,10 +10304,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10330,10 +10333,10 @@
         <v>354</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10384,7 +10387,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10408,7 +10411,7 @@
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10419,10 +10422,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10537,10 +10540,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10657,10 +10660,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10779,10 +10782,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10808,10 +10811,10 @@
         <v>196</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10841,10 +10844,10 @@
         <v>113</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>79</v>
@@ -10862,7 +10865,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10886,7 +10889,7 @@
         <v>79</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -10897,10 +10900,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10923,13 +10926,13 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10980,7 +10983,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>89</v>
@@ -11004,7 +11007,7 @@
         <v>79</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -11015,10 +11018,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11041,19 +11044,19 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>79</v>
@@ -11102,7 +11105,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11126,7 +11129,7 @@
         <v>79</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>79</v>
@@ -11137,10 +11140,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11166,13 +11169,13 @@
         <v>196</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11201,10 +11204,10 @@
         <v>200</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>79</v>
@@ -11222,7 +11225,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11246,7 +11249,7 @@
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -979,7 +979,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -979,7 +979,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1195,7 +1195,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1010,7 +1010,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/EncounterOutpatient)
+    <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
@@ -1195,7 +1195,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -682,7 +682,7 @@
     <t>http://hl7.org/fhir/ValueSet/procedure-category</t>
   </si>
   <si>
-    <t>1314: fixed value = http://snomed.info/sct#371883000 Outpatient procedure (procedure)</t>
+    <t>1314: fixed value = http://snomed.info/sct#371883000 "Outpatient procedure (procedure)"</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN</t>
   </si>
   <si>
-    <t>Encounter.EncounterExtension.Cpt,Encounter.EncounterExtension.Cpt,Procedure.Procedure,Procedure.CodeTableDetail.Procedure.Code</t>
+    <t>Encounter.Extension[EncounterExtension].Cpt,Encounter.Extension[EncounterExtension].Cpt,Procedure.Procedure,Procedure.Procedure[CodeTableDetail.Procedure].Code</t>
   </si>
   <si>
     <t>union(., ./translation)</t>
@@ -972,7 +972,7 @@
 Dim.ProviderNarrative.ProviderNarrative</t>
   </si>
   <si>
-    <t>Procedure.Procedure,Procedure.CodeTableDetail.Procedure.OriginalText</t>
+    <t>Procedure.Procedure,Procedure.Procedure[CodeTableDetail.Procedure].OriginalText</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -1038,7 +1038,7 @@
     <t>Outpat.VProcedure.VisitDateTime,Outpat.VProcedure.VisitIEN,Outpat.VProcedureCPTModifier.VisitDateTime,Outpat.VProcedureCPTModifier.VisitIEN,Outpat.VProcedureDiagnosis.VisitDateTime,Outpat.VProcedureDiagnosis.VisitIEN,Outpat.WorkloadVProcedure.VisitDateTime,Outpat.WorkloadVProcedure.VisitIEN,Outpat.WorkloadVProcedureCPTModifier.VisitDateTime,Outpat.WorkloadVProcedureCPTModifier.VisitIEN,Outpat.WorkloadVProcedureDiagnosis.VisitDateTime,Outpat.WorkloadVProcedureDiagnosis.VisitIEN</t>
   </si>
   <si>
-    <t>Procedure.EncounterNumber,Procedure.EnteredAt,Procedure.EnteredBy,Procedure.EnteredOn,Procedure.ProcedureExtension.Location</t>
+    <t>Procedure.EncounterNumber,Procedure.EnteredAt,Procedure.EnteredBy,Procedure.EnteredOn,Procedure.Extension[ProcedureExtension].Location</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1589,7 +1589,7 @@
     <t>Outpat.VProcedure.Comments,Outpat.WorkloadVProcedure.Comments</t>
   </si>
   <si>
-    <t>Procedure.ProcedureExtension.Comments</t>
+    <t>Procedure.Extension[ProcedureExtension].Comments</t>
   </si>
   <si>
     <t>Act.text</t>
@@ -2045,7 +2045,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="121.41796875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="126.40625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="158.0234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="142.56640625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file V CPT (9000010.18) to us-core-procedure</t>
+    <t>This StructureDefinition contains the maps for VistA file V CPT (9000010.18) to us-core-procedure.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -791,7 +791,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1413: source value from V CPT - CPT &gt; CPT (9000010.18-.01 &gt; 81-)</t>
+    <t>1413: source value based on V CPT - CPT &gt; CPT (9000010.18-.01 &gt; 81-)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN</t>
@@ -878,7 +878,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1413-1: source value from V CPT - CPT &gt; CPT - CPT CODE (9000010.18-.01 &gt; 81-.01)</t>
+    <t>1413-1: source value based on V CPT - CPT &gt; CPT - CPT CODE (9000010.18-.01 &gt; 81-.01)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN
@@ -906,7 +906,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1413-2: source value from V CPT - CPT &gt; CPT - SHORT NAME (9000010.18-.01 &gt; 81-2)</t>
+    <t>1413-2: source value based on V CPT - CPT &gt; CPT - SHORT NAME (9000010.18-.01 &gt; 81-2)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.CPTIEN,Outpat.VProcedureCPTModifier.CPTIEN,Outpat.VProcedureDiagnosis.CPTIEN,Outpat.WorkloadVProcedure.CPTIEN,Outpat.WorkloadVProcedureCPTModifier.CPTIEN,Outpat.WorkloadVProcedureDiagnosis.CPTIEN
@@ -965,7 +965,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1301: source value from V CPT - PROVIDER NARRATIVE &gt; PROVIDER NARRATIVE - NARRATIVE (9000010.18-.04 &gt; 9999999.27-.01)</t>
+    <t>1301: source value based on V CPT - PROVIDER NARRATIVE &gt; PROVIDER NARRATIVE - NARRATIVE (9000010.18-.04 &gt; 9999999.27-.01)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.ProviderNarrativeIEN,Outpat.WorkloadVProcedure.ProviderNarrativeIEN
@@ -998,7 +998,7 @@
     <t>The person, animal or group on which the procedure was performed.</t>
   </si>
   <si>
-    <t>1299: reference from V CPT - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.18-.02 &gt; 9000001-.01)</t>
+    <t>1299: reference based on V CPT - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.18-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.PatientIEN,Outpat.VProcedureCPTModifier.PatientIEN,Outpat.VProcedureDiagnosis.PatientIEN,Outpat.WorkloadVProcedure.PatientIEN,Outpat.WorkloadVProcedureCPTModifier.PatientIEN,Outpat.WorkloadVProcedureDiagnosis.PatientIEN</t>
@@ -1032,7 +1032,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
   </si>
   <si>
-    <t>1300: reference from V CPT - VISIT (9000010.18-.03)</t>
+    <t>1300: reference based on V CPT - VISIT (9000010.18-.03)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.VisitDateTime,Outpat.VProcedure.VisitIEN,Outpat.VProcedureCPTModifier.VisitDateTime,Outpat.VProcedureCPTModifier.VisitIEN,Outpat.VProcedureDiagnosis.VisitDateTime,Outpat.VProcedureDiagnosis.VisitIEN,Outpat.WorkloadVProcedure.VisitDateTime,Outpat.WorkloadVProcedure.VisitIEN,Outpat.WorkloadVProcedureCPTModifier.VisitDateTime,Outpat.WorkloadVProcedureCPTModifier.VisitIEN,Outpat.WorkloadVProcedureDiagnosis.VisitDateTime,Outpat.WorkloadVProcedureDiagnosis.VisitIEN</t>
@@ -1095,7 +1095,7 @@
 </t>
   </si>
   <si>
-    <t>1310: source value from V CPT - EVENT DATE AND TIME (9000010.18-1201)</t>
+    <t>1310: source value based on V CPT - EVENT DATE AND TIME (9000010.18-1201)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.EventDateTime,Outpat.VProcedureDiagnosis.EventDateTime,Outpat.WorkloadVProcedure.EventDateTime,Outpat.WorkloadVProcedureDiagnosis.EventDateTime</t>
@@ -1223,7 +1223,7 @@
     <t>A reference to Device supports use cases, such as pacemakers.</t>
   </si>
   <si>
-    <t>1311: reference from V CPT - ENCOUNTER PROVIDER (9000010.18-1204)</t>
+    <t>1311: reference based on V CPT - ENCOUNTER PROVIDER (9000010.18-1204)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.EncounterProviderIEN,Outpat.WorkloadVProcedure.EncounterProviderIEN</t>
@@ -1303,7 +1303,7 @@
     <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
   </si>
   <si>
-    <t>1309: source value from V CPT - DIAGNOSIS 8 &gt; ICD DIAGNOSIS (9000010.18-.15 &gt; 80-)</t>
+    <t>1309: source value based on V CPT - DIAGNOSIS 8 &gt; ICD DIAGNOSIS (9000010.18-.15 &gt; 80-)</t>
   </si>
   <si>
     <t>Outpat.VProcedureDiagnosis.ICDIEN,Outpat.WorkloadVProcedureDiagnosis.ICDIEN</t>
@@ -1348,7 +1348,7 @@
     <t>Procedure.reasonCode.coding.code</t>
   </si>
   <si>
-    <t>1309-2: source value from V CPT - DIAGNOSIS 8 &gt; ICD DIAGNOSIS - CODE NUMBER (9000010.18-.15 &gt; 80-.01)</t>
+    <t>1309-2: source value based on V CPT - DIAGNOSIS 8 &gt; ICD DIAGNOSIS - CODE NUMBER (9000010.18-.15 &gt; 80-.01)</t>
   </si>
   <si>
     <t>Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
@@ -1583,7 +1583,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1312: source value from V CPT - COMMENTS (9000010.18-81101)</t>
+    <t>1312: source value based on V CPT - COMMENTS (9000010.18-81101)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.Comments,Outpat.WorkloadVProcedure.Comments</t>
@@ -2043,7 +2043,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="121.41796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="125.51171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="158.0234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1019,7 +1019,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/EncounterOutpatient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatient.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
